--- a/Financial Analysis/AM.xlsx
+++ b/Financial Analysis/AM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505B2A9B-05A4-41E8-A2E1-5544E5BE9992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57075AA2-623A-4852-853F-4D13F83778EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{1BC9B113-5C36-4F33-A230-153587A19A07}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="71">
   <si>
     <t>AM</t>
   </si>
@@ -230,16 +230,26 @@
   </si>
   <si>
     <t>Overvalued</t>
+  </si>
+  <si>
+    <t>L+S/E</t>
+  </si>
+  <si>
+    <t>EV/B</t>
+  </si>
+  <si>
+    <t>B/EV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$€-2]\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,6 +282,15 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -318,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -337,6 +356,8 @@
     </xf>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -783,14 +804,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>27.18</v>
+        <v>28.96</v>
       </c>
       <c r="E3" s="5">
-        <v>45868</v>
+        <v>45934</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45868</v>
+        <v>45934</v>
       </c>
       <c r="G3" s="5">
         <v>46079</v>
@@ -813,7 +834,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>35695.493999999999</v>
+        <v>38033.167999999998</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -855,7 +876,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>34236.493999999999</v>
+        <v>36574.167999999998</v>
       </c>
     </row>
   </sheetData>
@@ -865,7 +886,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F60969-B396-4B2D-BA08-B794DFF6F5C3}">
-  <dimension ref="B2:EI39"/>
+  <dimension ref="B2:EI45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -4616,7 +4637,7 @@
       </c>
       <c r="AJ34" s="4">
         <f>Main!D3</f>
-        <v>27.18</v>
+        <v>28.96</v>
       </c>
     </row>
     <row r="35" spans="2:36" x14ac:dyDescent="0.3">
@@ -4736,7 +4757,7 @@
       </c>
       <c r="AJ35" s="11">
         <f>AJ33/AJ34-1</f>
-        <v>-0.43497641969139733</v>
+        <v>-0.46970507897832114</v>
       </c>
     </row>
     <row r="36" spans="2:36" x14ac:dyDescent="0.3">
@@ -5182,6 +5203,32 @@
         <v>0.22067936975465416</v>
       </c>
     </row>
+    <row r="42" spans="2:36" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="L42" s="12">
+        <v>14415.3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L44" s="13">
+        <f>Main!D9/Model!L42</f>
+        <v>2.537177027186392</v>
+      </c>
+    </row>
+    <row r="45" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L45" s="10">
+        <f>L42/Main!D9-1</f>
+        <v>-0.60586116408717761</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
